--- a/doctool/test/auto/scenario27/システム機能設計書_サンプル_S27_レビュー記録票_expected.xlsx
+++ b/doctool/test/auto/scenario27/システム機能設計書_サンプル_S27_レビュー記録票_expected.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" updateLinks="never" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C257D5-2471-43A6-A3A1-44F4E814E8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92250916-5B24-44C2-A8DB-08BBCB4ACF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/doctool/test/auto/scenario27/システム機能設計書_サンプル_S27_レビュー記録票_expected.xlsx
+++ b/doctool/test/auto/scenario27/システム機能設計書_サンプル_S27_レビュー記録票_expected.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" updateLinks="never" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92250916-5B24-44C2-A8DB-08BBCB4ACF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9343FD-2A61-4CF7-884C-1CB37731FE90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1381,7 +1381,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="220">
   <si>
     <t>レビュー対象物</t>
     <rPh sb="4" eb="7">
@@ -2673,6 +2673,19 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>91_疑問点、確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+疑問点・確認の指摘例（カテゴリg）。_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+改善要望の指摘例（カテゴリh）。_x000D_
+</t>
+  </si>
+  <si>
     <t>93_仕様変更</t>
   </si>
   <si>
@@ -2706,18 +2719,6 @@
   </si>
   <si>
     <t>詳細設計</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t xml:space="preserve">_x000D_
-疑問点・確認の指摘例（カテゴリg）。_x000D_
-</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t xml:space="preserve">_x000D_
-改善要望の指摘例（カテゴリh）。_x000D_
-</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4816,7 +4817,7 @@
       </c>
       <c r="B1" s="77"/>
       <c r="C1" s="90" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D1" s="91"/>
       <c r="E1" s="100" t="s">
@@ -5735,25 +5736,25 @@
         <v>1</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>104</v>
+        <v>208</v>
       </c>
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
       <c r="H11" s="27" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="I11" s="28" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K11" s="26"/>
       <c r="L11" s="28"/>
       <c r="M11" s="28" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="N11" s="30"/>
       <c r="O11" s="31"/>
@@ -5767,25 +5768,25 @@
         <v>1</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="D12" s="26"/>
       <c r="E12" s="26"/>
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
       <c r="H12" s="27" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J12" s="27" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="K12" s="26"/>
       <c r="L12" s="28"/>
       <c r="M12" s="28" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="N12" s="30"/>
       <c r="O12" s="31"/>
@@ -5799,14 +5800,14 @@
         <v>1</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="26"/>
       <c r="F13" s="26"/>
       <c r="G13" s="26"/>
       <c r="H13" s="27" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="I13" s="28" t="s">
         <v>193</v>
@@ -5831,14 +5832,14 @@
         <v>1</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D14" s="26"/>
       <c r="E14" s="26"/>
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
       <c r="H14" s="27" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I14" s="28" t="s">
         <v>193</v>
@@ -5863,14 +5864,14 @@
         <v>1</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D15" s="26"/>
       <c r="E15" s="26"/>
       <c r="F15" s="26"/>
       <c r="G15" s="26"/>
       <c r="H15" s="27" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I15" s="28" t="s">
         <v>193</v>
@@ -5895,14 +5896,14 @@
         <v>1</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D16" s="26"/>
       <c r="E16" s="26"/>
       <c r="F16" s="26"/>
       <c r="G16" s="26"/>
       <c r="H16" s="27" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I16" s="28" t="s">
         <v>193</v>
